--- a/artfynd/A 21742-2025 artfynd.xlsx
+++ b/artfynd/A 21742-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521466</v>
+        <v>121521465</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581389</v>
+        <v>581419</v>
       </c>
       <c r="R2" t="n">
-        <v>7048317</v>
+        <v>7048316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre hackspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521467</v>
+        <v>121521466</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581385</v>
+        <v>581389</v>
       </c>
       <c r="R3" t="n">
-        <v>7048323</v>
+        <v>7048317</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +871,416 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121521461</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>581453</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7048286</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121521462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>581449</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7048302</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 1 kvm</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121521468</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>581370</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7048349</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 1 kvm</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121521467</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>581385</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7048323</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21742-2025 artfynd.xlsx
+++ b/artfynd/A 21742-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521465</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521466</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521461</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521462</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521468</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,8 +1311,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121521467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>